--- a/Results/rbf_fd_parameter_study_4.xlsx
+++ b/Results/rbf_fd_parameter_study_4.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1053,6 +1053,721 @@
         <v>250</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D12" t="n">
+        <v>100</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.0007214906338283145</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.0001483566163465309</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2525902.842988192</v>
+      </c>
+      <c r="N12" t="n">
+        <v>7.778461252883062e-08</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.000078346744808e-07</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>100</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.1229371131558976</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.02513343045541504</v>
+      </c>
+      <c r="M13" t="n">
+        <v>27822598.45087831</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.232123992167544e-06</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.67652752065076e-06</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>100</v>
+      </c>
+      <c r="E14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>9.285181074547566e-05</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2.453216857575069e-05</v>
+      </c>
+      <c r="M14" t="n">
+        <v>212.3498936290216</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.0003105174861701698</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.0009743184571712493</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>100</v>
+      </c>
+      <c r="B15" t="n">
+        <v>100</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>100</v>
+      </c>
+      <c r="E15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.851973377904216e-06</v>
+      </c>
+      <c r="L15" t="n">
+        <v>5.739125897945389e-07</v>
+      </c>
+      <c r="M15" t="n">
+        <v>261.0122722952977</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.499109561109435e-05</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.077892734734916e-05</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>100</v>
+      </c>
+      <c r="B16" t="n">
+        <v>100</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>100</v>
+      </c>
+      <c r="E16" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H16" t="n">
+        <v>12</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>6.334342045821728e-05</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.347864557094102e-05</v>
+      </c>
+      <c r="M16" t="n">
+        <v>161.6467315488156</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.0002630440222048946</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.0006406984525075334</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>100</v>
+      </c>
+      <c r="B17" t="n">
+        <v>100</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>100</v>
+      </c>
+      <c r="E17" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H17" t="n">
+        <v>12</v>
+      </c>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.000281227408526763</v>
+      </c>
+      <c r="L17" t="n">
+        <v>6.386085442838245e-05</v>
+      </c>
+      <c r="M17" t="n">
+        <v>326.7649890175321</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.0009827717552184367</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.002343234025925132</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>100</v>
+      </c>
+      <c r="B18" t="n">
+        <v>100</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>100</v>
+      </c>
+      <c r="E18" t="n">
+        <v>10</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H18" t="n">
+        <v>12</v>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.0002613479051596368</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.0001170303808389782</v>
+      </c>
+      <c r="M18" t="n">
+        <v>164.5965847506257</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.00271225100675565</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.006848544340693018</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>100</v>
+      </c>
+      <c r="B19" t="n">
+        <v>100</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>100</v>
+      </c>
+      <c r="E19" t="n">
+        <v>10</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H19" t="n">
+        <v>12</v>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="b">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.002091020271770883</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.0005108436256868432</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1160.141804844674</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.00328207115568091</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.01510953239116321</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>100</v>
+      </c>
+      <c r="B20" t="n">
+        <v>100</v>
+      </c>
+      <c r="C20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" t="n">
+        <v>100</v>
+      </c>
+      <c r="E20" t="n">
+        <v>10</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H20" t="n">
+        <v>12</v>
+      </c>
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" t="b">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1.014133269272577e-05</v>
+      </c>
+      <c r="L20" t="n">
+        <v>3.290998344039261e-06</v>
+      </c>
+      <c r="M20" t="n">
+        <v>59.39533744951665</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.0003301178711865305</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.0002366840386700999</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>100</v>
+      </c>
+      <c r="B21" t="n">
+        <v>100</v>
+      </c>
+      <c r="C21" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>100</v>
+      </c>
+      <c r="E21" t="n">
+        <v>10</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H21" t="n">
+        <v>12</v>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" t="b">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.590478547994437e-05</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2.390872198369896e-05</v>
+      </c>
+      <c r="M21" t="n">
+        <v>107.7905438217784</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.0007850289338193761</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.001411287142336049</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>100</v>
+      </c>
+      <c r="B22" t="n">
+        <v>100</v>
+      </c>
+      <c r="C22" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D22" t="n">
+        <v>100</v>
+      </c>
+      <c r="E22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H22" t="n">
+        <v>12</v>
+      </c>
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.0007767760121595302</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.0004703951914674851</v>
+      </c>
+      <c r="M22" t="n">
+        <v>383.0969665850026</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.005765678818619335</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.02615532296699225</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>100</v>
+      </c>
+      <c r="B23" t="n">
+        <v>100</v>
+      </c>
+      <c r="C23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D23" t="n">
+        <v>100</v>
+      </c>
+      <c r="E23" t="n">
+        <v>10</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H23" t="n">
+        <v>12</v>
+      </c>
+      <c r="I23" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" t="b">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.0002000226870175759</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.0001178696834713915</v>
+      </c>
+      <c r="M23" t="n">
+        <v>34.2099699845242</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.01335196178774822</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.008807812625187858</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>100</v>
+      </c>
+      <c r="B24" t="n">
+        <v>100</v>
+      </c>
+      <c r="C24" t="n">
+        <v>15</v>
+      </c>
+      <c r="D24" t="n">
+        <v>100</v>
+      </c>
+      <c r="E24" t="n">
+        <v>10</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H24" t="n">
+        <v>12</v>
+      </c>
+      <c r="I24" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" t="b">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.001539033098018283</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.0001781009725330002</v>
+      </c>
+      <c r="M24" t="n">
+        <v>106.1398622907739</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.47663385636406</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.371387341540546</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Results/rbf_fd_parameter_study_4.xlsx
+++ b/Results/rbf_fd_parameter_study_4.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Stencil Nodes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1771,4 +1772,765 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.0001547085588644581</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.114103254403555e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.658735369776665</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.01091880870296791</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.007746463239885861</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.105948608681739e-05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>7.519586265108504e-06</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.7765416061555812</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.0001430320093049886</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0004370992911480748</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>40</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.283578415997802e-05</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.834784940365974e-05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>170.9999084452803</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.0003877071409306154</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.001034991152059645</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>50</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>5.758402830646769e-05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3.126040492889569e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>228.8821601867881</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.0007109148027666379</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.001840545204912776</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8.857980074727934e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>4.583725842149232e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>170.0419587527705</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.001021982024269619</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.002759525869663663</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>75</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0002027657470087263</v>
+      </c>
+      <c r="L7" t="n">
+        <v>6.451899461223026e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>110.1098616912553</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.001594351733032795</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.003962814110303083</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>85</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.01089997412687671</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.001617888002851872</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3938.674640490157</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.001930379662155701</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.005180122240542027</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0002613479051596368</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001170303808389782</v>
+      </c>
+      <c r="M9" t="n">
+        <v>164.5965847506257</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.00271225100675565</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.006848544340693018</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>115</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0005197554825189243</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.0001757384874118832</v>
+      </c>
+      <c r="M10" t="n">
+        <v>313.7038789692138</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.002495826185466399</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.009146221655225231</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>130</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.001034019425573129</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.0002665189692874366</v>
+      </c>
+      <c r="M11" t="n">
+        <v>514.9181454739006</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.00263546041506757</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.01090604397475178</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>150</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.001394315730148366</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.0002933128495654691</v>
+      </c>
+      <c r="M12" t="n">
+        <v>403.7231240137433</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.003463288291520428</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.01027085984231713</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>200</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.565497948163852e-05</v>
+      </c>
+      <c r="L13" t="n">
+        <v>4.479108333885569e-06</v>
+      </c>
+      <c r="M13" t="n">
+        <v>41.97137918577818</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.00070072986818559</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.0002573282508646319</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>200</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_4.xlsx
+++ b/Results/rbf_fd_parameter_study_4.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Stencil Nodes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Center Rings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2533,4 +2534,545 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.000283163283631982</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0001186765404608519</v>
+      </c>
+      <c r="M2" t="n">
+        <v>332.2160061092416</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.001907622722939095</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.006461724104593701</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0003716988412125755</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.000119548779048761</v>
+      </c>
+      <c r="M3" t="n">
+        <v>258.1236700736663</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.001899439173712381</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.006616456030548406</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0002627332592549658</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0001163581734064462</v>
+      </c>
+      <c r="M4" t="n">
+        <v>195.9788993626663</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.002677728139531155</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.006630908751698762</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0003585413654614289</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0001267603178285656</v>
+      </c>
+      <c r="M5" t="n">
+        <v>369.4140138604971</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.002040037235630621</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.006642359623272777</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.0002606842626795558</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0001240258616291229</v>
+      </c>
+      <c r="M6" t="n">
+        <v>156.9321198072275</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.002726496276807211</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.006844997753573054</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0002613479051596368</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0001170303808389782</v>
+      </c>
+      <c r="M7" t="n">
+        <v>164.5965847506257</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.00271225100675565</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.006848544340693018</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.0002504436431582935</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.0001196702556107406</v>
+      </c>
+      <c r="M8" t="n">
+        <v>89.23847055138572</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.002703836298934448</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.006847951695852859</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0003769132830200306</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.000122219646847248</v>
+      </c>
+      <c r="M9" t="n">
+        <v>124.6268391917636</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.002698569938729634</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.006839965942464271</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_4.xlsx
+++ b/Results/rbf_fd_parameter_study_4.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Stencil Nodes" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Center Rings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Eigenvalue Ratio" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3075,4 +3076,820 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.0002217414883276536</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0001070766687183193</v>
+      </c>
+      <c r="M2" t="n">
+        <v>129.1107687078122</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.02670718196554844</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.07431163210171758</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0002386148120461229</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.0001113309850844401</v>
+      </c>
+      <c r="M3" t="n">
+        <v>132.710677518532</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.01313548288317179</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.04027514217166658</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0002226092229022925</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.000106553762081431</v>
+      </c>
+      <c r="M4" t="n">
+        <v>116.5440925625477</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.002966005101086466</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.01325312066911856</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0002325063613710654</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0001081816497056033</v>
+      </c>
+      <c r="M5" t="n">
+        <v>120.2815451413758</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.002496294914138275</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.009972159918640767</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.0005094868985972001</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0001401266630963429</v>
+      </c>
+      <c r="M6" t="n">
+        <v>384.1601527508033</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.002670814029784196</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.007430990180135834</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0003722700099075826</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.000128016407059164</v>
+      </c>
+      <c r="M7" t="n">
+        <v>246.0609238603153</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.002692619833851495</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.007123034107805615</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.0002824763313218348</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.0001190572441170537</v>
+      </c>
+      <c r="M8" t="n">
+        <v>183.2473826438618</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.002710079523268405</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.006878908088814398</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0002613479051596368</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001170303808389782</v>
+      </c>
+      <c r="M9" t="n">
+        <v>164.5965847506257</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.00271225100675565</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.006848544340693018</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>100</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0002650784927100691</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.0001189189320159541</v>
+      </c>
+      <c r="M10" t="n">
+        <v>148.5351735557136</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.00271399689665941</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.00682427846861131</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>100</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0002819383432486333</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.0001199505533316298</v>
+      </c>
+      <c r="M11" t="n">
+        <v>155.1634992746978</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.002714213518714814</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.006821246846020742</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.0005</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>100</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.0003079952447275769</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.000121881565765989</v>
+      </c>
+      <c r="M12" t="n">
+        <v>168.9750170004945</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.002714388990000316</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.006818821712181276</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>100</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.0003129084487580869</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.0001223572731506518</v>
+      </c>
+      <c r="M13" t="n">
+        <v>171.954481614434</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.002714405114403462</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.006818518527134903</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>5e-05</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>100</v>
+      </c>
+      <c r="E14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.0003169380812584333</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.0001228297279250115</v>
+      </c>
+      <c r="M14" t="n">
+        <v>174.7886333555351</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.002714431905275205</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.006818276193009941</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>1e-05</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_4.xlsx
+++ b/Results/rbf_fd_parameter_study_4.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Stencil Nodes" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Center Rings" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Eigenvalue Ratio" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Eigenvector Angle" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3892,4 +3893,600 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.000320948112199293</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0001217864416822897</v>
+      </c>
+      <c r="M2" t="n">
+        <v>195.4844044352438</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.002712167159586443</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.006848734112169306</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0009835059284799552</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.0001690141041295088</v>
+      </c>
+      <c r="M3" t="n">
+        <v>441.567605811007</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.002015677015243966</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.006709154502478545</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.01347297877540488</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0006420979275461479</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2191.109674436657</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.002101982240020561</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.006662250680575928</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.00511909857343551</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0003556108866023059</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1246.991875140706</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.002015911738936893</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.006708821141441342</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.0002613479051596368</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0001170303808389782</v>
+      </c>
+      <c r="M6" t="n">
+        <v>164.5965847506257</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.00271225100675565</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.006848544340693018</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>16</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0004046260951640068</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0001378168006399261</v>
+      </c>
+      <c r="M7" t="n">
+        <v>192.2437351567264</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.002015895295770065</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.00671421154010251</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>18</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.001974023246682499</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.000213261972811138</v>
+      </c>
+      <c r="M8" t="n">
+        <v>593.4659884256845</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.002101985876876711</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.006668243240349044</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>20</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0004216263868646042</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001326008133533013</v>
+      </c>
+      <c r="M9" t="n">
+        <v>218.7601692461263</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.002015680510361051</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.006714071788208287</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>100</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>24</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0003209550217062596</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.0001217866497838319</v>
+      </c>
+      <c r="M10" t="n">
+        <v>195.4910098681202</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.002712167202759019</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.006848734103402027</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_4.xlsx
+++ b/Results/rbf_fd_parameter_study_4.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9FF79E7-4409-4773-8EE0-D6BD369CF13B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Grid Size" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,20 @@
     <sheet name="Eigenvalue Ratio" sheetId="4" r:id="rId5"/>
     <sheet name="Eigenvector Angle" sheetId="5" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 

--- a/Results/rbf_fd_parameter_study_4.xlsx
+++ b/Results/rbf_fd_parameter_study_4.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1056,4 +1057,930 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>5.15776761300657e-08</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.170149870699077e-08</v>
+      </c>
+      <c r="M2" t="n">
+        <v>403.667429830957</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.558888698127703e-07</v>
+      </c>
+      <c r="O2" t="n">
+        <v>4.59163949109803e-07</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>8.355480307642438e-08</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.515244924985477e-08</v>
+      </c>
+      <c r="M3" t="n">
+        <v>420.1220879496954</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.179108378186356e-07</v>
+      </c>
+      <c r="O3" t="n">
+        <v>4.650222889517684e-07</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.213602413629999e-05</v>
+      </c>
+      <c r="L4" t="n">
+        <v>5.754518974039994e-06</v>
+      </c>
+      <c r="M4" t="n">
+        <v>413.1980298390419</v>
+      </c>
+      <c r="N4" t="n">
+        <v>7.257112974912161e-05</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0003061393782945199</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.000182399545909373</v>
+      </c>
+      <c r="L5" t="n">
+        <v>8.979414303402367e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>394.2743112247418</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.001160870897138011</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.004897446871512496</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.423249436527385e-06</v>
+      </c>
+      <c r="L6" t="n">
+        <v>9.319257532052763e-07</v>
+      </c>
+      <c r="M6" t="n">
+        <v>227.9137419235733</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.945917049146374e-05</v>
+      </c>
+      <c r="O6" t="n">
+        <v>5.412034236137021e-05</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5.378114513732157e-06</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3.512163566099419e-06</v>
+      </c>
+      <c r="M7" t="n">
+        <v>225.8700272278678</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.000112039697455657</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0002047823501025113</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.730846398195762e-05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.022526380022233e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>106.7256389853111</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.0002814481385939871</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0006085799251485187</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.987673647487533e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.56296767992541e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>136.4788563655834</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.0004567555259882283</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.001491815610751129</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>8.170306158361562e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5.656856655911672e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>125.5444599218774</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.0009247531376104234</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.003266968995470195</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>30</v>
+      </c>
+      <c r="E11" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0003177529474787111</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.0002164515174191528</v>
+      </c>
+      <c r="M11" t="n">
+        <v>128.2162905204614</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.003517309826520432</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.0123897508375604</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>30</v>
+      </c>
+      <c r="E12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.0002183345370966316</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.991735823513992e-05</v>
+      </c>
+      <c r="M12" t="n">
+        <v>135.0710227060104</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.02136077396062319</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.01187596650508828</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" t="n">
+        <v>30</v>
+      </c>
+      <c r="E13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.0002058246952514331</v>
+      </c>
+      <c r="L13" t="n">
+        <v>5.560575359225106e-05</v>
+      </c>
+      <c r="M13" t="n">
+        <v>19.99914776224824</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.6385502243065275</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.09240496002715831</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>15</v>
+      </c>
+      <c r="D14" t="n">
+        <v>30</v>
+      </c>
+      <c r="E14" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.0006398556608158135</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.0004201906221926254</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.317745344954783</v>
+      </c>
+      <c r="N14" t="n">
+        <v>15.7646698479075</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.718275275800662</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>100</v>
+      </c>
+      <c r="B15" t="n">
+        <v>100</v>
+      </c>
+      <c r="C15" t="n">
+        <v>20</v>
+      </c>
+      <c r="D15" t="n">
+        <v>30</v>
+      </c>
+      <c r="E15" t="n">
+        <v>12</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.006874373180758342</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.004697124773462093</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.472406017616031</v>
+      </c>
+      <c r="N15" t="n">
+        <v>101.3687872204464</v>
+      </c>
+      <c r="O15" t="n">
+        <v>10.87073161646969</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>100</v>
+      </c>
+      <c r="B16" t="n">
+        <v>100</v>
+      </c>
+      <c r="C16" t="n">
+        <v>30</v>
+      </c>
+      <c r="D16" t="n">
+        <v>30</v>
+      </c>
+      <c r="E16" t="n">
+        <v>12</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H16" t="n">
+        <v>12</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.1915165325475841</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.1317245893435265</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2.122936799894261</v>
+      </c>
+      <c r="N16" t="n">
+        <v>160.6572100292251</v>
+      </c>
+      <c r="O16" t="n">
+        <v>34.01707178461257</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_4.xlsx
+++ b/Results/rbf_fd_parameter_study_4.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1983,4 +1984,875 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.02095996009633594</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.001099681826573512</v>
+      </c>
+      <c r="M2" t="n">
+        <v>100.4794019094472</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.03437745505175371</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.02435551677006257</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6.186426187371197e-05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>4.206032990415095e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.378919570722259</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.0006653603288100385</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.002432910079934021</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>40</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0001947681314047323</v>
+      </c>
+      <c r="L4" t="n">
+        <v>8.718918901942909e-05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>215.3750642750604</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.001938929142227153</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.005111571901537764</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>50</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0003478605170155191</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0001697703518488743</v>
+      </c>
+      <c r="M5" t="n">
+        <v>238.3959499958031</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.003983140533790674</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.01015438056296416</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.003217267372429777</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0006284607564758944</v>
+      </c>
+      <c r="M6" t="n">
+        <v>929.5728401976429</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.005059867107121363</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.01482936556421971</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>75</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.001346768740133064</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0004184102097423872</v>
+      </c>
+      <c r="M7" t="n">
+        <v>248.4575190293482</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.005791448650569464</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.02015442535998347</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>85</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.00835516740739517</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.001852428171695177</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3894.550033943378</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.005898320346062746</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.02693607682460013</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0005856801625256924</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001381333123490433</v>
+      </c>
+      <c r="M9" t="n">
+        <v>5943.592037151979</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.003354418916146074</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.002268340809744104</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>115</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.958492710829596e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>6.631667651817829e-06</v>
+      </c>
+      <c r="M10" t="n">
+        <v>62.90187920735139</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.0006186318578329519</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0004035214894400074</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>130</v>
+      </c>
+      <c r="E11" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.446121571986204e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>9.189737200396046e-06</v>
+      </c>
+      <c r="M11" t="n">
+        <v>45.27081534811753</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.0006337468004886659</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.000589865869163767</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>150</v>
+      </c>
+      <c r="E12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.0001746056500717685</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.829227028339486e-05</v>
+      </c>
+      <c r="M12" t="n">
+        <v>174.228998800169</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.0008777296189066419</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.0009358562819601004</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>175</v>
+      </c>
+      <c r="E13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.903967360725403e-05</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.125121837833363e-05</v>
+      </c>
+      <c r="M13" t="n">
+        <v>46.52455978411883</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.0007053114614024025</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.00132579877789111</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>200</v>
+      </c>
+      <c r="E14" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.0001929833581617579</v>
+      </c>
+      <c r="L14" t="n">
+        <v>4.447970014102989e-05</v>
+      </c>
+      <c r="M14" t="n">
+        <v>43.19968947621328</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.001221500327744707</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.002167016310717219</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>100</v>
+      </c>
+      <c r="B15" t="n">
+        <v>100</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>250</v>
+      </c>
+      <c r="E15" t="n">
+        <v>12</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.0003581386629263328</v>
+      </c>
+      <c r="L15" t="n">
+        <v>9.275217214828763e-05</v>
+      </c>
+      <c r="M15" t="n">
+        <v>118.253304797364</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.00153245632318999</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.003686553885623724</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>250</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_4.xlsx
+++ b/Results/rbf_fd_parameter_study_4.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Center Rings" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2855,4 +2856,655 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>8.217024072632029e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>5.682670768206551e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>124.0862618024664</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.0009245778333024646</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.003253658040077645</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>8.206369033181282e-05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>5.681429334660363e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>124.9078313776046</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.0009245465361118477</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.003253534596649039</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>8.207434080964582e-05</v>
+      </c>
+      <c r="L4" t="n">
+        <v>5.681416374104209e-05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>125.4023123395894</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.0009245487036650957</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.003253535056492199</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>8.207913779734177e-05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>5.681189980120023e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>125.2473197931128</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.0009245877797638968</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.00325338284294843</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8.207373272617335e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>5.681645012644916e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>125.3851283552024</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.0009246275083114597</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.003253586043143071</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>8.301684160838541e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>5.681801464733136e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>126.3850055007906</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.000924657641576232</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.003266717766321462</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>8.254778480898395e-05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>5.678644683544358e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>126.0209582406003</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.0009247153398064256</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.003266880962236102</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>8.170306158361562e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5.656856655911672e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>125.5444599218774</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.0009247531376104234</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.003266968995470195</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" t="n">
+        <v>13</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>8.321079290385391e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5.688107069965389e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>126.6083979677539</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.0009247780483292445</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.003268838013709936</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>30</v>
+      </c>
+      <c r="E11" t="n">
+        <v>14</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>9.08436816130509e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5.756811470115781e-05</v>
+      </c>
+      <c r="M11" t="n">
+        <v>135.4000693309706</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.0009248061376183614</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.003269240710133214</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_4.xlsx
+++ b/Results/rbf_fd_parameter_study_4.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Center Rings" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Eigenvalue Ratio" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3507,4 +3508,820 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>8.834764808751672e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>5.377485361605367e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>120.805868904163</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.00992069181666011</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.03575260200607646</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>9.109761600534227e-05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>5.314642373693649e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>119.0060475510258</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.005314742807058792</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.01949919983871134</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>9.552507473853389e-05</v>
+      </c>
+      <c r="L4" t="n">
+        <v>5.277654553056464e-05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>117.9439028951546</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.001630032596494857</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.00649826562656127</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>9.942880310920277e-05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>5.25399164392731e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>149.441137578525</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.001275597625181035</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.004873960577577517</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.0002877913720863434</v>
+      </c>
+      <c r="L6" t="n">
+        <v>8.139528207489253e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1825.448170555317</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.000992086204178122</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.003575231806572432</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>8.717397282498318e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>5.392744960146392e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>132.3966332134844</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.0009566473094082539</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.003412976192864494</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>8.237904750751923e-05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>5.609699701799996e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>124.8824171240667</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.0009282968578645523</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.003283191408737816</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>8.170306158361562e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5.656856655911672e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>125.5444599218774</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.0009247531376104234</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.003266968995470195</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>9.879896920050868e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5.763756426416206e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>144.0021556554438</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.000921918132121391</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.003253991940162176</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>30</v>
+      </c>
+      <c r="E11" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>9.841074709560083e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5.767645751082309e-05</v>
+      </c>
+      <c r="M11" t="n">
+        <v>134.0909334896033</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.0009215636949875261</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.003252370164398994</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.0005</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>30</v>
+      </c>
+      <c r="E12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.0001140936549692828</v>
+      </c>
+      <c r="L12" t="n">
+        <v>5.792303469279603e-05</v>
+      </c>
+      <c r="M12" t="n">
+        <v>132.4371342999585</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.0009212802069669124</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.003251072169296382</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>30</v>
+      </c>
+      <c r="E13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.0001172273325551476</v>
+      </c>
+      <c r="L13" t="n">
+        <v>5.798090544361769e-05</v>
+      </c>
+      <c r="M13" t="n">
+        <v>132.4989569392637</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.000921244717233094</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.003250909824377467</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>5e-05</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>30</v>
+      </c>
+      <c r="E14" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.0001200242173382549</v>
+      </c>
+      <c r="L14" t="n">
+        <v>5.803502678458273e-05</v>
+      </c>
+      <c r="M14" t="n">
+        <v>132.5945559731424</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.0009212163821530339</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.003250780238564881</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>1e-05</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_4.xlsx
+++ b/Results/rbf_fd_parameter_study_4.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Center Rings" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Eigenvalue Ratio" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Eigenvector Angle" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4324,4 +4325,600 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>8.357695652283503e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>5.639413315202793e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>127.7985404329596</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.0009247354856825041</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.003266999933990501</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0001141405952154173</v>
+      </c>
+      <c r="L3" t="n">
+        <v>6.066793589887477e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>136.0995325461495</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.001092782548369087</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.003266739161925222</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0001457708692021997</v>
+      </c>
+      <c r="L4" t="n">
+        <v>6.629598270298885e-05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>127.9774989529763</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.00107411528023249</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.003266754822346951</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.000112229136867481</v>
+      </c>
+      <c r="L5" t="n">
+        <v>6.099913859719899e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>126.6359957794153</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.001092786666561096</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.003266665050742675</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8.170306158361562e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>5.656856655911672e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>125.5444599218774</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.0009247531376104234</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.003266968995470195</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>16</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0001107746462070125</v>
+      </c>
+      <c r="L7" t="n">
+        <v>6.036799341737024e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>126.6417257424473</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.001092799388572985</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.00326836830199373</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>18</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.0001621783099761132</v>
+      </c>
+      <c r="L8" t="n">
+        <v>6.87303864447538e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>184.2721501528801</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.001074129243079369</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.003268654168772414</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>20</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001105805874446197</v>
+      </c>
+      <c r="L9" t="n">
+        <v>6.024575225622385e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>126.6800808858998</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.001092785894513781</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.003268325935012474</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>24</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>8.357696642269374e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5.639413398438612e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>127.7985571297134</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.00092473548295402</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.003266999935084519</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_4.xlsx
+++ b/Results/rbf_fd_parameter_study_4.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1166,4 +1167,930 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>500</v>
+      </c>
+      <c r="B2" t="n">
+        <v>500</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3.311685551565154</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.091711703819725</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1200242911.302499</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.005005000010410862</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.05590172744882795</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>500</v>
+      </c>
+      <c r="B3" t="n">
+        <v>500</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.311261253180237</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.091662135226351</v>
+      </c>
+      <c r="M3" t="n">
+        <v>299977928.1049027</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.02002000016657379</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.223606911190682</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>500</v>
+      </c>
+      <c r="B4" t="n">
+        <v>500</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.863216174236015e-06</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.337190455574189e-06</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.1425501160166688</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.490639988332987e-05</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0001664868159577555</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>500</v>
+      </c>
+      <c r="B5" t="n">
+        <v>500</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>7.816814229233415e-07</v>
+      </c>
+      <c r="L5" t="n">
+        <v>4.41959629404885e-07</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.01182596091309171</v>
+      </c>
+      <c r="N5" t="n">
+        <v>6.255810149013996e-06</v>
+      </c>
+      <c r="O5" t="n">
+        <v>5.717999295808116e-05</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>500</v>
+      </c>
+      <c r="B6" t="n">
+        <v>500</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>7.352640539304289e-06</v>
+      </c>
+      <c r="L6" t="n">
+        <v>5.276809342773481e-06</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.03516182722795411</v>
+      </c>
+      <c r="N6" t="n">
+        <v>5.884625716134906e-05</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0006569244463434726</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>500</v>
+      </c>
+      <c r="B7" t="n">
+        <v>500</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.92960729874514e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.384773311523691e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.05905632255003775</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.000154410838149488</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.001723936753962392</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>500</v>
+      </c>
+      <c r="B8" t="n">
+        <v>500</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.030492806972319e-05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.892732595392739e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.08567276695707056</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.000322512409184128</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.003601170429890659</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>500</v>
+      </c>
+      <c r="B9" t="n">
+        <v>500</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>7.461579149503628e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5.355448890227763e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.1165330524311969</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.0005969643534626812</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.006667024193570084</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>500</v>
+      </c>
+      <c r="B10" t="n">
+        <v>500</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0001276811450532378</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9.16423377527654e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.1526788246118056</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.001021432311972603</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0114082801876759</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>500</v>
+      </c>
+      <c r="B11" t="n">
+        <v>500</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0003116751709399956</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.0002237008818402708</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2385405046038181</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.002493163192411885</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.02784472028450949</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>500</v>
+      </c>
+      <c r="B12" t="n">
+        <v>500</v>
+      </c>
+      <c r="C12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.00157886224163506</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.001133169583039474</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.5371728977573448</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.0126174472970888</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.1409231835763661</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>500</v>
+      </c>
+      <c r="B13" t="n">
+        <v>500</v>
+      </c>
+      <c r="C13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.005003317688015541</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.003590583158666412</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.9577425184395167</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.03987646693713032</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.4453865418859634</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>500</v>
+      </c>
+      <c r="B14" t="n">
+        <v>500</v>
+      </c>
+      <c r="C14" t="n">
+        <v>15</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.02574927042063746</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.01846739853687821</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.19109436028063</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.2018506468448322</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.25450453721258</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>500</v>
+      </c>
+      <c r="B15" t="n">
+        <v>500</v>
+      </c>
+      <c r="C15" t="n">
+        <v>20</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.0852487991591353</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.06103837415208568</v>
+      </c>
+      <c r="M15" t="n">
+        <v>4.077098165575977</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.6378400576068088</v>
+      </c>
+      <c r="O15" t="n">
+        <v>7.124147790435013</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>500</v>
+      </c>
+      <c r="B16" t="n">
+        <v>500</v>
+      </c>
+      <c r="C16" t="n">
+        <v>30</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H16" t="n">
+        <v>12</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.6019842231273715</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.4263782809823824</v>
+      </c>
+      <c r="M16" t="n">
+        <v>12.66850821747111</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.227514276717557</v>
+      </c>
+      <c r="O16" t="n">
+        <v>36.04867574187172</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_4.xlsx
+++ b/Results/rbf_fd_parameter_study_4.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2093,4 +2094,600 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>500</v>
+      </c>
+      <c r="B2" t="n">
+        <v>500</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.0001276811450532378</v>
+      </c>
+      <c r="L2" t="n">
+        <v>9.16423377527654e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.1526788246118056</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.001021432311972603</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0114082801876759</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>500</v>
+      </c>
+      <c r="B3" t="n">
+        <v>500</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0001277560837071867</v>
+      </c>
+      <c r="L3" t="n">
+        <v>9.169600154670727e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.1539217610790295</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.001022088828904089</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.01141495088417166</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>500</v>
+      </c>
+      <c r="B4" t="n">
+        <v>500</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0002983058525307669</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0002136840743549013</v>
+      </c>
+      <c r="M4" t="n">
+        <v>727.1024505203828</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.00238198068109341</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0266043495404692</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>500</v>
+      </c>
+      <c r="B5" t="n">
+        <v>500</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.001380399551208056</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.000536626242615603</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2147.839354146932</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.005247005985438591</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.05437586037338468</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>500</v>
+      </c>
+      <c r="B6" t="n">
+        <v>500</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.002124305738844701</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0005712317990504492</v>
+      </c>
+      <c r="M6" t="n">
+        <v>6344.709190050578</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.006560782316228142</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.06540460314860921</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>500</v>
+      </c>
+      <c r="B7" t="n">
+        <v>500</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>25</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.001984458750743823</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0007963860690533123</v>
+      </c>
+      <c r="M7" t="n">
+        <v>17523.43059892921</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.01048027046999778</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.09601881577647473</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>500</v>
+      </c>
+      <c r="B8" t="n">
+        <v>500</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>40</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.03244859463999006</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.005685887787869708</v>
+      </c>
+      <c r="M8" t="n">
+        <v>13474.56700955724</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.01816653474816121</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.1392214935614177</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>500</v>
+      </c>
+      <c r="B9" t="n">
+        <v>500</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>50</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.007710683947917074</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.002141631683032642</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2896.082929199318</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.02714363273844356</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.1862547721488509</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>500</v>
+      </c>
+      <c r="B10" t="n">
+        <v>500</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>65</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.02379519014620635</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.003929013117454814</v>
+      </c>
+      <c r="M10" t="n">
+        <v>6546.504339258173</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.0356159584271154</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.2298350384261636</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_4.xlsx
+++ b/Results/rbf_fd_parameter_study_4.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Center Rings" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2690,4 +2691,655 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>500</v>
+      </c>
+      <c r="B2" t="n">
+        <v>500</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.0001276811450532378</v>
+      </c>
+      <c r="L2" t="n">
+        <v>9.16423377527654e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.1526788246118056</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.001021432311972603</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0114082801876759</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>500</v>
+      </c>
+      <c r="B3" t="n">
+        <v>500</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0001279349606464475</v>
+      </c>
+      <c r="L3" t="n">
+        <v>9.182465262071055e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.1532405191028177</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.001023491000523791</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.01143097337543634</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>500</v>
+      </c>
+      <c r="B4" t="n">
+        <v>500</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0001278180116537353</v>
+      </c>
+      <c r="L4" t="n">
+        <v>9.168134857861854e-05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.1530767384171352</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.001022651209495962</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.01141316409454467</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>500</v>
+      </c>
+      <c r="B5" t="n">
+        <v>500</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0001276975099411271</v>
+      </c>
+      <c r="L5" t="n">
+        <v>9.165218110910274e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.1531383335949991</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.001021617965307087</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.01140949469793331</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>500</v>
+      </c>
+      <c r="B6" t="n">
+        <v>500</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.0001275403771472394</v>
+      </c>
+      <c r="L6" t="n">
+        <v>9.154064561062861e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.1529941018201698</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.001020302821416408</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.01139562906958221</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>500</v>
+      </c>
+      <c r="B7" t="n">
+        <v>500</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0001275418389317107</v>
+      </c>
+      <c r="L7" t="n">
+        <v>9.15409697788747e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.1530016868087787</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.001020321913529187</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.01139564993007679</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>500</v>
+      </c>
+      <c r="B8" t="n">
+        <v>500</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.0001275806680467451</v>
+      </c>
+      <c r="L8" t="n">
+        <v>9.156944357118001e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.153082910567451</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.001020627649268135</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.01139919977665101</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>500</v>
+      </c>
+      <c r="B9" t="n">
+        <v>500</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001276532553782239</v>
+      </c>
+      <c r="L9" t="n">
+        <v>9.162225171583514e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.1532292819734227</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.001021286618197337</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.01140577252730061</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>500</v>
+      </c>
+      <c r="B10" t="n">
+        <v>500</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>13</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0001275471140622653</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9.152837154531054e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.1531109735407114</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.001020822965074331</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.01139413350339305</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>500</v>
+      </c>
+      <c r="B11" t="n">
+        <v>500</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>14</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.000127511815480208</v>
+      </c>
+      <c r="L11" t="n">
+        <v>9.146347996605826e-05</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.1530200822759246</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.001021470467094332</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.01138594511081755</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_4.xlsx
+++ b/Results/rbf_fd_parameter_study_4.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Center Rings" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Eigenvalue Ratio" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3342,4 +3343,820 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>500</v>
+      </c>
+      <c r="B2" t="n">
+        <v>500</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.0001382405350751625</v>
+      </c>
+      <c r="L2" t="n">
+        <v>8.543124326855932e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.1446014559465764</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.01122044562362134</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.1253181091622164</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>500</v>
+      </c>
+      <c r="B3" t="n">
+        <v>500</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0001436002026449223</v>
+      </c>
+      <c r="L3" t="n">
+        <v>8.462975294527958e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.1430884190596855</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.006120417267084122</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.06835750249282242</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>500</v>
+      </c>
+      <c r="B4" t="n">
+        <v>500</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.000150320993200781</v>
+      </c>
+      <c r="L4" t="n">
+        <v>8.402306088771385e-05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.1415389593187124</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.002040412800852209</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.02278900916735302</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>500</v>
+      </c>
+      <c r="B5" t="n">
+        <v>500</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0001489953209985462</v>
+      </c>
+      <c r="L5" t="n">
+        <v>8.412627280815492e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.1418486133746497</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.001530412759166211</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.01709294991078496</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>500</v>
+      </c>
+      <c r="B6" t="n">
+        <v>500</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.0001382878068487692</v>
+      </c>
+      <c r="L6" t="n">
+        <v>8.546045296906833e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.1446706001574288</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.001122412330005318</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.01253609995931391</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>500</v>
+      </c>
+      <c r="B7" t="n">
+        <v>500</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0001336829029014996</v>
+      </c>
+      <c r="L7" t="n">
+        <v>8.657700404124155e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.1464074933670761</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.001071412290912122</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.01196649521927975</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>500</v>
+      </c>
+      <c r="B8" t="n">
+        <v>500</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.0001288285949472279</v>
+      </c>
+      <c r="L8" t="n">
+        <v>8.930356645068392e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.1499620330520968</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.001030612358590588</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.01151080878066948</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>500</v>
+      </c>
+      <c r="B9" t="n">
+        <v>500</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001281912019945874</v>
+      </c>
+      <c r="L9" t="n">
+        <v>9.02233806444494e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.151055431229229</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.001025512348860502</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.01145384916006684</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>500</v>
+      </c>
+      <c r="B10" t="n">
+        <v>500</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0001276811450532378</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9.16423377527654e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.1526788246118056</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.001021432311972603</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0114082801876759</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>500</v>
+      </c>
+      <c r="B11" t="n">
+        <v>500</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0001276173849908968</v>
+      </c>
+      <c r="L11" t="n">
+        <v>9.201196009068096e-05</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.1530896685941797</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.001020922412863001</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.01140258419441115</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.0005</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>500</v>
+      </c>
+      <c r="B12" t="n">
+        <v>500</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.0001275663754602974</v>
+      </c>
+      <c r="L12" t="n">
+        <v>9.252349988598091e-05</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.1536454465381192</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.001020514435367659</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.01139802694058171</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>500</v>
+      </c>
+      <c r="B13" t="n">
+        <v>500</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.0001275599993917353</v>
+      </c>
+      <c r="L13" t="n">
+        <v>9.264604844325521e-05</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.153774448323784</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.001020463358145207</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.01139745726360383</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>5e-05</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>500</v>
+      </c>
+      <c r="B14" t="n">
+        <v>500</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.0001275549066830362</v>
+      </c>
+      <c r="L14" t="n">
+        <v>9.280210977009394e-05</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.1539345975119474</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.001020422583678737</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.01139700186164085</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>1e-05</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_4.xlsx
+++ b/Results/rbf_fd_parameter_study_4.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Center Rings" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Eigenvalue Ratio" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Eigenvector Angle" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4159,4 +4160,600 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>500</v>
+      </c>
+      <c r="B2" t="n">
+        <v>500</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.0001276280609725511</v>
+      </c>
+      <c r="L2" t="n">
+        <v>9.160413874275073e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.1525898319104256</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.00102102744858712</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.01140351928311817</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>500</v>
+      </c>
+      <c r="B3" t="n">
+        <v>500</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0001470355834958248</v>
+      </c>
+      <c r="L3" t="n">
+        <v>8.427410943615065e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.1422573843213576</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.001021132033201866</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.01140473567312089</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>500</v>
+      </c>
+      <c r="B4" t="n">
+        <v>500</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0001503213907274592</v>
+      </c>
+      <c r="L4" t="n">
+        <v>8.402328369594384e-05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.1415394098968232</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.001021231015329249</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.01140592945143892</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>500</v>
+      </c>
+      <c r="B5" t="n">
+        <v>500</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.000147066245561378</v>
+      </c>
+      <c r="L5" t="n">
+        <v>8.429168028584916e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.1422988392722878</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.001021331903757527</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.01140711574528015</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>500</v>
+      </c>
+      <c r="B6" t="n">
+        <v>500</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.0001276811450532378</v>
+      </c>
+      <c r="L6" t="n">
+        <v>9.16423377527654e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.1526788246118056</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.001021432311972603</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0114082801876759</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>500</v>
+      </c>
+      <c r="B7" t="n">
+        <v>500</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H7" t="n">
+        <v>16</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0001470655758502026</v>
+      </c>
+      <c r="L7" t="n">
+        <v>8.429129604318812e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.1422980943231643</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.001021327218040824</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.01140706363375641</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>500</v>
+      </c>
+      <c r="B8" t="n">
+        <v>500</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H8" t="n">
+        <v>18</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.00015032060255038</v>
+      </c>
+      <c r="L8" t="n">
+        <v>8.402284189783715e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.1415385163703142</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.001021225703880191</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.01140586924874732</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>500</v>
+      </c>
+      <c r="B9" t="n">
+        <v>500</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H9" t="n">
+        <v>20</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001470349188159581</v>
+      </c>
+      <c r="L9" t="n">
+        <v>8.427372637310335e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.142256591801456</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.001021127478452399</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.01140468366067523</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>500</v>
+      </c>
+      <c r="B10" t="n">
+        <v>500</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>24</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0001276280609725511</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9.160413874275073e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.1525898319104256</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.00102102744858712</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.01140351928311817</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>